--- a/data/source-workbooks/main-source.xlsx
+++ b/data/source-workbooks/main-source.xlsx
@@ -1772,12 +1772,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="F2" s="63" t="n">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="F3" s="63" t="n">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="F4" s="63" t="n">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="F5" s="63" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="F6" s="63" t="n">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="F7" s="63" t="n">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="F8" s="63" t="n">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="F9" s="63" t="n">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="F10" s="63" t="n">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="F11" s="63" t="n">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="F12" s="63" t="n">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH 44308</t>
+          <t>1040 Demo Street, Akron, OH 44308</t>
         </is>
       </c>
       <c r="F13" s="63" t="n">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9011,12 +9011,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="E6" s="32">
@@ -16893,12 +16893,12 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="E7" s="32">
@@ -16947,12 +16947,12 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="E8" s="32">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="E9" s="32">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="E10" s="32">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="E11" s="32">
@@ -17163,12 +17163,12 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="E12" s="32">
@@ -17217,12 +17217,12 @@
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="E13" s="32">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="E14" s="32">
@@ -17325,12 +17325,12 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="E15" s="32">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="E16" s="32">
@@ -23456,12 +23456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23496,12 +23496,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -23536,12 +23536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -23576,12 +23576,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -23656,12 +23656,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -23696,12 +23696,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -23776,12 +23776,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -23816,12 +23816,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -23896,12 +23896,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -23936,12 +23936,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -23976,12 +23976,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24016,12 +24016,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -24056,12 +24056,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -24096,12 +24096,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -24136,12 +24136,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -24176,12 +24176,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -24216,12 +24216,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -24256,12 +24256,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -24296,12 +24296,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -24336,12 +24336,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -24376,12 +24376,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -24416,12 +24416,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -24456,12 +24456,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -24496,12 +24496,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -24536,12 +24536,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -24576,12 +24576,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -24616,12 +24616,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -24656,12 +24656,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -24696,12 +24696,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -24736,12 +24736,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -24776,12 +24776,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -24816,12 +24816,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -24856,12 +24856,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -24896,12 +24896,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -24976,12 +24976,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -25016,12 +25016,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -25056,12 +25056,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -25096,12 +25096,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -25136,12 +25136,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -25256,12 +25256,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -25296,12 +25296,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -25336,12 +25336,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -25376,12 +25376,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -25416,12 +25416,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -25456,12 +25456,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -25496,12 +25496,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -25536,12 +25536,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -25576,12 +25576,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -25616,12 +25616,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -25656,12 +25656,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -25696,12 +25696,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -25736,12 +25736,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -25776,12 +25776,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -25816,12 +25816,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -25856,12 +25856,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -25896,12 +25896,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -25936,12 +25936,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -25976,12 +25976,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -26016,12 +26016,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -26096,12 +26096,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -26136,12 +26136,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -26216,12 +26216,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -26296,12 +26296,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -26336,12 +26336,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -26376,12 +26376,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -26416,12 +26416,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -26496,12 +26496,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -26536,12 +26536,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -26576,12 +26576,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -26616,12 +26616,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -26656,12 +26656,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -26696,12 +26696,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -26736,12 +26736,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -26776,12 +26776,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
